--- a/diseases/d023/2015-2019.xlsx
+++ b/diseases/d023/2015-2019.xlsx
@@ -1209,9 +1209,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1602,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2789,9 +2783,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3973,9 +3964,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -5157,9 +5145,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -6489,9 +6474,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -7673,9 +7655,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -8857,9 +8836,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -10189,9 +10165,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -11373,9 +11346,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -12557,9 +12527,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -13889,9 +13856,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -15073,9 +15037,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -16257,9 +16218,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -16801,9 +16759,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -17985,9 +17940,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -19169,9 +19121,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -20501,9 +20450,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -21685,9 +21631,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -22869,9 +22812,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -24201,9 +24141,6 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -25385,9 +25322,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -26569,9 +26503,6 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
@@ -27901,9 +27832,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -29085,9 +29013,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -30269,9 +30194,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -31601,9 +31523,6 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0</v>
       </c>
@@ -31997,9 +31916,6 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
@@ -33181,9 +33097,6 @@
       <c r="O219" t="n">
         <v>0</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0</v>
       </c>
@@ -34365,9 +34278,6 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0</v>
       </c>
@@ -35697,9 +35607,6 @@
       <c r="O236" t="n">
         <v>0</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0</v>
       </c>
@@ -36881,9 +36788,6 @@
       <c r="O244" t="n">
         <v>0</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0</v>
       </c>
@@ -38065,9 +37969,6 @@
       <c r="O252" t="n">
         <v>0</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0</v>
       </c>
@@ -39397,9 +39298,6 @@
       <c r="O261" t="n">
         <v>0</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0</v>
       </c>
@@ -40581,9 +40479,6 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0</v>
       </c>
@@ -41913,9 +41808,6 @@
       <c r="O278" t="n">
         <v>0</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0</v>
       </c>
@@ -43097,9 +42989,6 @@
       <c r="O286" t="n">
         <v>0</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0</v>
       </c>
@@ -44281,9 +44170,6 @@
       <c r="O294" t="n">
         <v>0</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0</v>
       </c>
@@ -45613,9 +45499,6 @@
       <c r="O303" t="n">
         <v>0</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0</v>
       </c>
@@ -46797,9 +46680,6 @@
       <c r="O311" t="n">
         <v>0</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0</v>
       </c>
@@ -47193,9 +47073,6 @@
       <c r="O313" t="n">
         <v>0</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0</v>
       </c>
@@ -48377,9 +48254,6 @@
       <c r="O321" t="n">
         <v>0</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0</v>
       </c>
@@ -49561,9 +49435,6 @@
       <c r="O329" t="n">
         <v>0</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0</v>
       </c>
@@ -50893,9 +50764,6 @@
       <c r="O338" t="n">
         <v>0</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>0</v>
       </c>
@@ -52077,9 +51945,6 @@
       <c r="O346" t="n">
         <v>0</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
       <c r="R346" t="n">
         <v>0</v>
       </c>
@@ -53409,9 +53274,6 @@
       <c r="O355" t="n">
         <v>0</v>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>0</v>
       </c>
@@ -54593,9 +54455,6 @@
       <c r="O363" t="n">
         <v>0</v>
       </c>
-      <c r="Q363" t="n">
-        <v>0</v>
-      </c>
       <c r="R363" t="n">
         <v>0</v>
       </c>
@@ -55777,9 +55636,6 @@
       <c r="O371" t="n">
         <v>0</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0</v>
       </c>
@@ -57109,9 +56965,6 @@
       <c r="O380" t="n">
         <v>0</v>
       </c>
-      <c r="Q380" t="n">
-        <v>0</v>
-      </c>
       <c r="R380" t="n">
         <v>0</v>
       </c>
@@ -58293,9 +58146,6 @@
       <c r="O388" t="n">
         <v>0</v>
       </c>
-      <c r="Q388" t="n">
-        <v>0</v>
-      </c>
       <c r="R388" t="n">
         <v>0</v>
       </c>
@@ -59477,9 +59327,6 @@
       <c r="O396" t="n">
         <v>0</v>
       </c>
-      <c r="Q396" t="n">
-        <v>0</v>
-      </c>
       <c r="R396" t="n">
         <v>0</v>
       </c>
@@ -60809,9 +60656,6 @@
       <c r="O405" t="n">
         <v>0</v>
       </c>
-      <c r="Q405" t="n">
-        <v>0</v>
-      </c>
       <c r="R405" t="n">
         <v>0</v>
       </c>
@@ -61993,9 +61837,6 @@
       <c r="O413" t="n">
         <v>0</v>
       </c>
-      <c r="Q413" t="n">
-        <v>0</v>
-      </c>
       <c r="R413" t="n">
         <v>0</v>
       </c>
@@ -62389,9 +62230,6 @@
       <c r="O415" t="n">
         <v>0</v>
       </c>
-      <c r="Q415" t="n">
-        <v>0</v>
-      </c>
       <c r="R415" t="n">
         <v>0</v>
       </c>
@@ -63721,9 +63559,6 @@
       <c r="O424" t="n">
         <v>0</v>
       </c>
-      <c r="Q424" t="n">
-        <v>0</v>
-      </c>
       <c r="R424" t="n">
         <v>0</v>
       </c>
@@ -64905,9 +64740,6 @@
       <c r="O432" t="n">
         <v>0</v>
       </c>
-      <c r="Q432" t="n">
-        <v>0</v>
-      </c>
       <c r="R432" t="n">
         <v>0</v>
       </c>
@@ -66089,9 +65921,6 @@
       <c r="O440" t="n">
         <v>0</v>
       </c>
-      <c r="Q440" t="n">
-        <v>0</v>
-      </c>
       <c r="R440" t="n">
         <v>0</v>
       </c>
@@ -67273,9 +67102,6 @@
       <c r="O448" t="n">
         <v>0</v>
       </c>
-      <c r="Q448" t="n">
-        <v>0</v>
-      </c>
       <c r="R448" t="n">
         <v>0</v>
       </c>
@@ -68605,9 +68431,6 @@
       <c r="O457" t="n">
         <v>0</v>
       </c>
-      <c r="Q457" t="n">
-        <v>0</v>
-      </c>
       <c r="R457" t="n">
         <v>0</v>
       </c>
@@ -69789,9 +69612,6 @@
       <c r="O465" t="n">
         <v>0</v>
       </c>
-      <c r="Q465" t="n">
-        <v>0</v>
-      </c>
       <c r="R465" t="n">
         <v>0</v>
       </c>
@@ -70973,9 +70793,6 @@
       <c r="O473" t="n">
         <v>0</v>
       </c>
-      <c r="Q473" t="n">
-        <v>0</v>
-      </c>
       <c r="R473" t="n">
         <v>0</v>
       </c>
@@ -72305,9 +72122,6 @@
       <c r="O482" t="n">
         <v>0</v>
       </c>
-      <c r="Q482" t="n">
-        <v>0</v>
-      </c>
       <c r="R482" t="n">
         <v>0</v>
       </c>
@@ -73489,9 +73303,6 @@
       <c r="O490" t="n">
         <v>0</v>
       </c>
-      <c r="Q490" t="n">
-        <v>0</v>
-      </c>
       <c r="R490" t="n">
         <v>0</v>
       </c>
@@ -74821,9 +74632,6 @@
       <c r="O499" t="n">
         <v>0</v>
       </c>
-      <c r="Q499" t="n">
-        <v>0</v>
-      </c>
       <c r="R499" t="n">
         <v>0</v>
       </c>
@@ -76003,9 +75811,6 @@
         <v>0</v>
       </c>
       <c r="O507" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q507" t="n">
         <v>0</v>
       </c>
       <c r="R507" t="n">
